--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2746,8 +2746,8 @@
       <c r="S20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T20" s="9" t="n">
-        <v>0</v>
+      <c r="T20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U20" s="9" t="n">
         <v>0</v>
@@ -11391,13 +11391,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>5</v>
@@ -11678,7 +11678,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>

--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2361,7 +2365,11 @@
       <c r="AB16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2983,7 +2991,11 @@
       <c r="AB22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3294,7 +3306,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3601,7 +3617,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -4009,7 +4029,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4110,7 +4134,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -5027,7 +5055,11 @@
       <c r="AB42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -6061,7 +6093,11 @@
       <c r="AB52" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6263,7 +6299,11 @@
       <c r="AB54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -7386,7 +7426,11 @@
       <c r="AB65" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC65" s="4" t="inlineStr"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -8000,7 +8044,11 @@
       <c r="AB71" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8408,7 +8456,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8509,7 +8561,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -10347,7 +10403,11 @@
       <c r="AB94" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -10850,7 +10910,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">

--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 43 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3999,8 +3999,8 @@
       <c r="R32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="9" t="n">
-        <v>1</v>
+      <c r="S32" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T32" s="10" t="n">
         <v>1</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9780,8 +9780,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -10542,13 +10542,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11410,8 +11410,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -11841,7 +11841,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -12270,7 +12270,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12369,7 +12369,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1532,8 +1532,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1821,8 +1821,8 @@
       <c r="S11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="9" t="n">
-        <v>0</v>
+      <c r="T11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U11" s="9" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2045,8 +2045,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2560,8 +2560,8 @@
       <c r="W18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X18" s="9" t="n">
-        <v>3</v>
+      <c r="X18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3402,8 +3402,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
@@ -3713,8 +3713,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -4406,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4537,8 +4537,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4612,7 +4612,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y38" s="9" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5979,8 +5979,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6063,8 +6063,8 @@
       <c r="R52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S52" s="9" t="n">
-        <v>1</v>
+      <c r="S52" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T52" s="9" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6395,8 +6395,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6601,8 +6601,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -7009,8 +7009,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7522,8 +7522,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -8290,13 +8290,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8346,8 +8346,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="9" t="n">
         <v>0</v>
@@ -8964,8 +8964,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="9" t="n">
         <v>0</v>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9150,7 +9150,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" s="9" t="n">
         <v>0</v>
@@ -9170,8 +9170,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9578,8 +9578,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10188,8 +10188,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10598,8 +10598,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10699,8 +10699,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -11404,8 +11404,8 @@
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="9" t="n">
-        <v>2</v>
+      <c r="X104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -11643,7 +11643,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -11676,7 +11676,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11775,7 +11775,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -11808,7 +11808,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11874,7 +11874,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11973,7 +11973,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12006,7 +12006,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12039,7 +12039,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12072,7 +12072,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12105,7 +12105,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12204,7 +12204,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12237,7 +12237,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12303,7 +12303,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12336,7 +12336,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -963,20 +963,20 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -984,7 +984,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1068,20 +1068,20 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1089,7 +1089,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1181,12 +1181,12 @@
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1194,7 +1194,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1274,20 +1274,20 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1295,7 +1295,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1318,11 +1318,11 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>1</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="9" t="n">
         <v>1</v>
@@ -1375,20 +1375,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1396,13 +1396,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>0</v>
@@ -1476,20 +1476,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1497,7 +1497,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1577,20 +1577,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1598,7 +1598,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1682,20 +1682,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1703,7 +1703,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1783,20 +1783,20 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1804,7 +1804,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1888,20 +1888,20 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1909,7 +1909,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1989,20 +1989,20 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -2010,7 +2010,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2033,11 +2033,11 @@
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="9" t="n">
-        <v>0</v>
+      <c r="V13" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W13" s="10" t="n">
+        <v>13</v>
       </c>
       <c r="X13" s="9" t="n">
         <v>3</v>
@@ -2090,20 +2090,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2111,7 +2111,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2195,20 +2195,20 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2216,7 +2216,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2239,11 +2239,11 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>3</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>5</v>
@@ -2300,20 +2300,20 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2321,7 +2321,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2405,20 +2405,20 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2426,7 +2426,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2510,20 +2510,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2531,13 +2531,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>0</v>
@@ -2615,20 +2615,20 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2636,13 +2636,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2716,20 +2716,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2737,7 +2737,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2821,20 +2821,20 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2842,7 +2842,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2926,20 +2926,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2947,7 +2947,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3031,20 +3031,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -3052,7 +3052,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3079,7 +3079,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3114,15 +3114,15 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>5940461</v>
+        <v>4402590</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Orange Nation</t>
+          <t>Roncesvalles Speakers Circle</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3136,20 +3136,20 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -3157,13 +3157,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -3174,20 +3174,20 @@
       <c r="S24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="9" t="n">
-        <v>0</v>
+      <c r="T24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>0</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y24" s="9" t="n">
         <v>0</v>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -3219,15 +3219,15 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4402590</v>
+        <v>2876712</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Roncesvalles Speakers Circle</t>
+          <t>TELUS House of Speakers</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3241,20 +3241,20 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3271,7 +3271,7 @@
         <v>2</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>0</v>
@@ -3285,14 +3285,14 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="10" t="n">
-        <v>4</v>
+      <c r="V25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
@@ -3304,13 +3304,9 @@
         <v>1</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC25" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3324,15 +3320,15 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2876712</v>
+        <v>5940461</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>TELUS House of Speakers</t>
+          <t>Wider World Toastmasters</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3346,20 +3342,20 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
+        <v>-12</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3367,16 +3363,16 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" s="9" t="n">
         <v>0</v>
@@ -3384,8 +3380,8 @@
       <c r="S26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T26" s="10" t="n">
-        <v>1</v>
+      <c r="T26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U26" s="9" t="n">
         <v>0</v>
@@ -3397,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="X26" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y26" s="9" t="n">
         <v>0</v>
@@ -3409,9 +3405,13 @@
         <v>1</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3447,20 +3447,20 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3468,7 +3468,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3552,20 +3552,20 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3573,7 +3573,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3597,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3657,20 +3657,20 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3678,7 +3678,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3758,20 +3758,20 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3779,7 +3779,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3859,20 +3859,20 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3880,7 +3880,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3903,8 +3903,8 @@
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>3</v>
+      <c r="V31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3977,7 +3977,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3985,7 +3985,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4069,20 +4069,20 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -4090,7 +4090,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4105,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" s="10" t="n">
         <v>1</v>
@@ -4174,20 +4174,20 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -4195,7 +4195,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4275,20 +4275,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4296,7 +4296,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4376,20 +4376,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M36" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4397,7 +4397,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4481,20 +4481,20 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4502,7 +4502,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4582,20 +4582,20 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4603,7 +4603,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4683,20 +4683,20 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
+        <v>-12</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4704,7 +4704,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4784,20 +4784,20 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
+        <v>-11</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4805,7 +4805,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4885,20 +4885,20 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4906,7 +4906,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4990,20 +4990,20 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M42" s="7" t="n">
+      <c r="M42" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -5011,7 +5011,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5034,11 +5034,11 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>2</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>4</v>
@@ -5081,7 +5081,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5095,20 +5095,20 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>7</v>
+        <v>-7</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -5116,7 +5116,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5142,8 +5142,8 @@
       <c r="V43" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W43" s="9" t="n">
-        <v>3</v>
+      <c r="W43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>6</v>
@@ -5200,20 +5200,20 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -5221,7 +5221,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5314,7 +5314,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5322,7 +5322,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5402,20 +5402,20 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5423,7 +5423,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5507,20 +5507,20 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5528,7 +5528,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5612,20 +5612,20 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5633,7 +5633,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5660,7 +5660,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>4</v>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5717,20 +5717,20 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5738,7 +5738,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5746,14 +5746,14 @@
       <c r="P49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" s="9" t="n">
-        <v>1</v>
+      <c r="Q49" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="10" t="n">
         <v>1</v>
@@ -5761,11 +5761,11 @@
       <c r="U49" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V49" s="9" t="n">
-        <v>1</v>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W49" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>5</v>
@@ -5822,20 +5822,20 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5843,7 +5843,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5923,20 +5923,20 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M51" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5944,7 +5944,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6028,20 +6028,20 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>3</v>
+        <v>-14</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M52" s="7" t="n">
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -6049,7 +6049,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6133,20 +6133,20 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -6154,7 +6154,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6234,20 +6234,20 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>4</v>
+        <v>-12</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -6255,7 +6255,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6282,7 +6282,7 @@
         <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>7</v>
@@ -6339,20 +6339,20 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M55" s="7" t="n">
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6360,7 +6360,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6384,7 +6384,7 @@
         <v>1</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6444,20 +6444,20 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6465,7 +6465,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6545,20 +6545,20 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L57" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M57" s="7" t="n">
+      <c r="M57" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6566,7 +6566,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6589,11 +6589,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>2</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>5</v>
@@ -6646,20 +6646,20 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="M58" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6667,7 +6667,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6747,20 +6747,20 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="M59" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6768,7 +6768,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6848,20 +6848,20 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6869,7 +6869,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6953,20 +6953,20 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="M61" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6974,7 +6974,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7040,7 +7040,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7054,20 +7054,20 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M62" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -7075,7 +7075,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7098,11 +7098,11 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>3</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>6</v>
@@ -7167,12 +7167,12 @@
       <c r="K63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L63" s="8" t="inlineStr">
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -7180,7 +7180,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7268,12 +7268,12 @@
       <c r="K64" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L64" s="8" t="inlineStr">
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M64" s="7" t="n">
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -7281,7 +7281,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7361,20 +7361,20 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -7382,7 +7382,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7405,11 +7405,11 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>3</v>
+      <c r="V65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X65" s="10" t="n">
         <v>6</v>
@@ -7466,20 +7466,20 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7487,7 +7487,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7567,20 +7567,20 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="M67" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7588,7 +7588,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7672,20 +7672,20 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7693,7 +7693,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7773,20 +7773,20 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7794,7 +7794,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7817,8 +7817,8 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>1</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7874,20 +7874,20 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M70" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7895,7 +7895,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7979,20 +7979,20 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>5</v>
+        <v>-11</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -8000,7 +8000,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8015,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T71" s="10" t="n">
         <v>1</v>
@@ -8084,20 +8084,20 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="M72" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -8105,7 +8105,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8185,20 +8185,20 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M73" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -8206,7 +8206,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8290,20 +8290,20 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -8311,7 +8311,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8334,8 +8334,8 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>3</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8391,20 +8391,20 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M75" s="7" t="n">
+      <c r="M75" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -8412,7 +8412,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8436,7 +8436,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8496,20 +8496,20 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8517,7 +8517,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8601,20 +8601,20 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="M77" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8622,7 +8622,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8702,20 +8702,20 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M78" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8723,7 +8723,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8807,20 +8807,20 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M79" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8828,7 +8828,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8851,8 +8851,8 @@
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="9" t="n">
-        <v>3</v>
+      <c r="V79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8908,20 +8908,20 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="M80" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8929,7 +8929,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8953,7 +8953,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -9009,20 +9009,20 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M81" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M81" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -9030,7 +9030,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9114,20 +9114,20 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -9135,7 +9135,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9158,11 +9158,11 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" s="9" t="n">
-        <v>0</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W82" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>5</v>
@@ -9215,20 +9215,20 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M83" s="7" t="n">
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -9236,7 +9236,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9260,7 +9260,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9316,20 +9316,20 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M84" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -9337,7 +9337,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9421,20 +9421,20 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M85" s="7" t="n">
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -9442,7 +9442,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9466,7 +9466,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9522,20 +9522,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M86" s="7" t="n">
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9543,7 +9543,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9566,11 +9566,11 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>0</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="9" t="n">
         <v>0</v>
@@ -9623,20 +9623,20 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="8" t="inlineStr">
+        <v>-12</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="M87" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9644,7 +9644,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9724,20 +9724,20 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M88" s="7" t="n">
+      <c r="M88" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9745,7 +9745,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9829,20 +9829,20 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="8" t="inlineStr">
+        <v>-18</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="M89" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9850,7 +9850,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9930,20 +9930,20 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L90" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9951,7 +9951,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9981,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="X90" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -10039,12 +10039,12 @@
       <c r="K91" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L91" s="8" t="inlineStr">
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -10052,7 +10052,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10132,20 +10132,20 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M92" s="7" t="n">
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -10153,7 +10153,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10233,20 +10233,20 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -10254,7 +10254,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10338,20 +10338,20 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M94" s="7" t="n">
+      <c r="M94" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -10359,7 +10359,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10386,7 +10386,7 @@
         <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>6</v>
@@ -10443,20 +10443,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="M95" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -10464,7 +10464,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10488,13 +10488,13 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X95" s="9" t="n">
-        <v>3</v>
+      <c r="X95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10542,20 +10542,20 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M96" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M96" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -10563,7 +10563,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10586,11 +10586,11 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>1</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>6</v>
@@ -10643,20 +10643,20 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M97" s="7" t="n">
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10664,7 +10664,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10688,7 +10688,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10744,20 +10744,20 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M98" s="7" t="n">
+      <c r="M98" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10765,7 +10765,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10845,20 +10845,20 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M99" s="7" t="n">
+      <c r="M99" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10866,7 +10866,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10950,20 +10950,20 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M100" s="7" t="n">
+      <c r="M100" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10971,7 +10971,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11051,20 +11051,20 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M101" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M101" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -11072,7 +11072,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="O101" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11096,7 +11096,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11152,20 +11152,20 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="M102" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -11173,7 +11173,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11253,20 +11253,20 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M103" s="7" t="n">
+      <c r="M103" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -11274,7 +11274,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11354,20 +11354,20 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="M104" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -11375,7 +11375,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="8" t="inlineStr">
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11399,7 +11399,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11455,20 +11455,20 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M105" s="7" t="n">
+      <c r="M105" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -11476,7 +11476,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11502,8 +11502,8 @@
       <c r="V105" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W105" s="9" t="n">
-        <v>3</v>
+      <c r="W105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>5</v>
@@ -11610,7 +11610,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -11676,7 +11676,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -11709,7 +11709,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -11724,7 +11724,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -11790,7 +11790,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -11808,7 +11808,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11823,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -11889,7 +11889,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -11907,7 +11907,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -11973,13 +11973,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -12021,7 +12021,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -12039,7 +12039,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12072,7 +12072,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12087,7 +12087,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -12105,7 +12105,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12120,7 +12120,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -12138,7 +12138,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -12153,7 +12153,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -12171,7 +12171,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12186,7 +12186,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -12204,7 +12204,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12219,7 +12219,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -12237,7 +12237,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12252,7 +12252,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -12303,7 +12303,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12318,7 +12318,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -12369,7 +12369,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -12384,7 +12384,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/60/inyear.xlsx
+++ b/docs/d/60/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="9" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1882,17 +1882,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -3235,13 +3235,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>4</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>2</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" s="9" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6171,11 +6171,11 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>3</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>4</v>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6374,8 +6374,8 @@
       <c r="T55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U55" s="9" t="n">
-        <v>0</v>
+      <c r="U55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V55" s="10" t="n">
         <v>4</v>
@@ -7460,17 +7460,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L66" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-13</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M66" s="7" t="n">
@@ -7565,13 +7565,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="10" t="n">
         <v>2</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="9" t="n">
         <v>0</v>
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
@@ -9213,13 +9213,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>1</v>
@@ -9261,7 +9261,7 @@
         <v>4</v>
       </c>
       <c r="W83" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>5</v>
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9314,13 +9314,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -9358,8 +9358,8 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>2</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -10437,13 +10437,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>6</v>
@@ -11150,13 +11150,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11823,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -12138,13 +12138,13 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -12252,7 +12252,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -12369,7 +12369,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
